--- a/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
+++ b/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="184">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -550,6 +550,30 @@
   </si>
   <si>
     <t>L01,L02,L04,L05,L07,L09.. L13,L15,L16,L17</t>
+  </si>
+  <si>
+    <t>Reteta(1,null)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reteta(1, [{apa,0.0}] </t>
+  </si>
+  <si>
+    <t>stoc=[]</t>
+  </si>
+  <si>
+    <t>Reteta(1, [{apa,100},{zahar,200}])</t>
+  </si>
+  <si>
+    <t>stoc:[apa=200,zahar=50]</t>
+  </si>
+  <si>
+    <t>stoc:[apa=100]</t>
+  </si>
+  <si>
+    <t>stoc:[apa=0]</t>
+  </si>
+  <si>
+    <t>Reteta(1,[{apa,-5.0}])</t>
   </si>
 </sst>
 </file>
@@ -809,19 +833,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1011,17 +1022,6 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="double">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="double">
         <color indexed="64"/>
       </bottom>
@@ -1165,11 +1165,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1190,52 +1210,49 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1243,203 +1260,214 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1879,16 +1907,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B1" s="12"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="11"/>
+      <c r="D1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="40"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="48"/>
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="33" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1906,21 +1934,21 @@
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N5" s="31" t="s">
+      <c r="N5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="O5" s="31"/>
-      <c r="P5" s="31"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="30"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26" t="s">
+      <c r="N6" s="25"/>
+      <c r="O6" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="P6" s="26" t="s">
+      <c r="P6" s="25" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1929,13 +1957,13 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="N7" s="26" t="s">
+      <c r="N7" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="O7" s="26" t="s">
+      <c r="O7" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="P7" s="26">
+      <c r="P7" s="25">
         <v>234</v>
       </c>
     </row>
@@ -1944,13 +1972,13 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="N8" s="26" t="s">
+      <c r="N8" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="O8" s="26" t="s">
+      <c r="O8" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="P8" s="26">
+      <c r="P8" s="25">
         <v>234</v>
       </c>
     </row>
@@ -1961,13 +1989,13 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="N9" s="26" t="s">
+      <c r="N9" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="O9" s="26" t="s">
+      <c r="O9" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="P9" s="26">
+      <c r="P9" s="25">
         <v>234</v>
       </c>
     </row>
@@ -1980,7 +2008,7 @@
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="32" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="1"/>
@@ -2024,434 +2052,434 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B1" s="12"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="11"/>
+      <c r="D1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="40"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="48"/>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
-      <c r="J3" s="85"/>
-      <c r="K3" s="86"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="I6" s="46" t="s">
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="I6" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="Q6" s="46" t="s">
+      <c r="J6" s="47"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="47"/>
+      <c r="Q6" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="R6" s="39"/>
-      <c r="S6" s="39"/>
-      <c r="T6" s="39"/>
+      <c r="R6" s="47"/>
+      <c r="S6" s="47"/>
+      <c r="T6" s="47"/>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B8" s="93">
+      <c r="B8" s="41">
         <v>1</v>
       </c>
-      <c r="C8" s="94" t="s">
+      <c r="C8" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="95"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="I8" s="12"/>
-      <c r="Q8" s="45" t="s">
+      <c r="D8" s="59"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="I8" s="11"/>
+      <c r="Q8" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="R8" s="39"/>
-      <c r="S8" s="40"/>
-      <c r="T8" s="30">
+      <c r="R8" s="47"/>
+      <c r="S8" s="48"/>
+      <c r="T8" s="29">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B9" s="31">
+      <c r="B9" s="30">
         <v>2</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="C9" s="49" t="s">
         <v>131</v>
       </c>
-      <c r="D9" s="87"/>
-      <c r="E9" s="88"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="37"/>
-      <c r="Q9" s="45" t="s">
+      <c r="D9" s="50"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="Q9" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="R9" s="39"/>
-      <c r="S9" s="40"/>
-      <c r="T9" s="30" t="s">
+      <c r="R9" s="47"/>
+      <c r="S9" s="48"/>
+      <c r="T9" s="29" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B10" s="31">
+      <c r="B10" s="30">
         <v>3</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="39"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="I10" s="92"/>
-      <c r="J10" s="92"/>
-      <c r="K10" s="92"/>
-      <c r="L10" s="92"/>
-      <c r="M10" s="92"/>
-      <c r="N10" s="92"/>
-      <c r="O10" s="92"/>
-      <c r="Q10" s="45" t="s">
+      <c r="D10" s="47"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="40"/>
+      <c r="Q10" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="R10" s="39"/>
-      <c r="S10" s="40"/>
-      <c r="T10" s="30" t="s">
+      <c r="R10" s="47"/>
+      <c r="S10" s="48"/>
+      <c r="T10" s="29" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B11" s="31"/>
-      <c r="C11" s="43" t="s">
+      <c r="B11" s="30"/>
+      <c r="C11" s="49" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="87"/>
-      <c r="E11" s="88"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="I11" s="92"/>
-      <c r="J11" s="92"/>
-      <c r="K11" s="92"/>
-      <c r="L11" s="92"/>
-      <c r="M11" s="92"/>
-      <c r="N11" s="92"/>
-      <c r="O11" s="92"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="40"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40"/>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B12" s="31">
+      <c r="B12" s="30">
         <v>4</v>
       </c>
-      <c r="C12" s="43" t="s">
+      <c r="C12" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="87"/>
-      <c r="E12" s="88"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="I12" s="92"/>
-      <c r="J12" s="92"/>
-      <c r="K12" s="92"/>
-      <c r="L12" s="92"/>
-      <c r="M12" s="92"/>
-      <c r="N12" s="92"/>
-      <c r="O12" s="92"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="40"/>
+      <c r="M12" s="40"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="40"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B13" s="31">
+      <c r="B13" s="30">
         <v>5</v>
       </c>
-      <c r="C13" s="43" t="s">
+      <c r="C13" s="49" t="s">
         <v>133</v>
       </c>
-      <c r="D13" s="87"/>
-      <c r="E13" s="88"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="I13" s="92"/>
-      <c r="J13" s="92"/>
-      <c r="K13" s="92"/>
-      <c r="L13" s="92"/>
-      <c r="M13" s="92"/>
-      <c r="N13" s="92"/>
-      <c r="O13" s="92"/>
-      <c r="Q13" s="46" t="s">
+      <c r="D13" s="50"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="40"/>
+      <c r="N13" s="40"/>
+      <c r="O13" s="40"/>
+      <c r="Q13" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="R13" s="39"/>
-      <c r="S13" s="39"/>
-      <c r="T13" s="39"/>
+      <c r="R13" s="47"/>
+      <c r="S13" s="47"/>
+      <c r="T13" s="47"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B14" s="31">
+      <c r="B14" s="30">
         <v>6</v>
       </c>
-      <c r="C14" s="43" t="s">
+      <c r="C14" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="87"/>
-      <c r="E14" s="88"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="I14" s="92"/>
-      <c r="J14" s="92"/>
-      <c r="K14" s="92"/>
-      <c r="L14" s="92"/>
-      <c r="M14" s="92"/>
-      <c r="N14" s="92"/>
-      <c r="O14" s="92"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="40"/>
+      <c r="M14" s="40"/>
+      <c r="N14" s="40"/>
+      <c r="O14" s="40"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B15" s="35"/>
-      <c r="C15" s="43" t="s">
+      <c r="B15" s="34"/>
+      <c r="C15" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="87"/>
-      <c r="E15" s="88"/>
-      <c r="I15" s="92"/>
-      <c r="J15" s="92"/>
-      <c r="K15" s="92"/>
-      <c r="L15" s="92"/>
-      <c r="M15" s="92"/>
-      <c r="N15" s="92"/>
-      <c r="O15" s="92"/>
-      <c r="Q15" s="31" t="s">
+      <c r="D15" s="50"/>
+      <c r="E15" s="51"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="40"/>
+      <c r="L15" s="40"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="40"/>
+      <c r="Q15" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R15" s="43" t="s">
+      <c r="R15" s="49" t="s">
         <v>145</v>
       </c>
-      <c r="S15" s="39"/>
-      <c r="T15" s="40"/>
+      <c r="S15" s="47"/>
+      <c r="T15" s="48"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B16" s="35">
+      <c r="B16" s="34">
         <v>7</v>
       </c>
-      <c r="C16" s="43" t="s">
+      <c r="C16" s="49" t="s">
         <v>134</v>
       </c>
-      <c r="D16" s="87"/>
-      <c r="E16" s="88"/>
-      <c r="I16" s="92"/>
-      <c r="J16" s="92"/>
-      <c r="K16" s="92"/>
-      <c r="L16" s="92"/>
-      <c r="M16" s="92"/>
-      <c r="N16" s="92"/>
-      <c r="O16" s="92"/>
-      <c r="Q16" s="31" t="s">
+      <c r="D16" s="50"/>
+      <c r="E16" s="51"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="40"/>
+      <c r="M16" s="40"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="40"/>
+      <c r="Q16" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="R16" s="43" t="s">
+      <c r="R16" s="49" t="s">
         <v>144</v>
       </c>
-      <c r="S16" s="39"/>
-      <c r="T16" s="40"/>
+      <c r="S16" s="47"/>
+      <c r="T16" s="48"/>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B17" s="35">
+      <c r="B17" s="34">
         <v>6</v>
       </c>
-      <c r="C17" s="43" t="s">
+      <c r="C17" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="87"/>
-      <c r="E17" s="88"/>
-      <c r="I17" s="92"/>
-      <c r="J17" s="92"/>
-      <c r="K17" s="92"/>
-      <c r="L17" s="92"/>
-      <c r="M17" s="92"/>
-      <c r="N17" s="92"/>
-      <c r="O17" s="92"/>
-      <c r="Q17" s="31" t="s">
+      <c r="D17" s="50"/>
+      <c r="E17" s="51"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="40"/>
+      <c r="L17" s="40"/>
+      <c r="M17" s="40"/>
+      <c r="N17" s="40"/>
+      <c r="O17" s="40"/>
+      <c r="Q17" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="R17" s="43" t="s">
+      <c r="R17" s="49" t="s">
         <v>146</v>
       </c>
-      <c r="S17" s="39"/>
-      <c r="T17" s="40"/>
+      <c r="S17" s="47"/>
+      <c r="T17" s="48"/>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B18" s="35"/>
-      <c r="C18" s="43" t="s">
+      <c r="B18" s="34"/>
+      <c r="C18" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="87"/>
-      <c r="E18" s="88"/>
-      <c r="I18" s="92"/>
-      <c r="J18" s="92"/>
-      <c r="K18" s="92"/>
-      <c r="L18" s="92"/>
-      <c r="M18" s="92"/>
-      <c r="N18" s="92"/>
-      <c r="O18" s="92"/>
-      <c r="Q18" s="101" t="s">
+      <c r="D18" s="50"/>
+      <c r="E18" s="51"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="40"/>
+      <c r="L18" s="40"/>
+      <c r="M18" s="40"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="40"/>
+      <c r="Q18" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="R18" s="102" t="s">
+      <c r="R18" s="54" t="s">
         <v>174</v>
       </c>
-      <c r="S18" s="103"/>
-      <c r="T18" s="104"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="56"/>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="34" t="s">
         <v>141</v>
       </c>
-      <c r="C19" s="43" t="s">
+      <c r="C19" s="49" t="s">
         <v>135</v>
       </c>
-      <c r="D19" s="87"/>
-      <c r="E19" s="88"/>
-      <c r="I19" s="92"/>
-      <c r="J19" s="92"/>
-      <c r="K19" s="92"/>
-      <c r="L19" s="92"/>
-      <c r="M19" s="92"/>
-      <c r="N19" s="92"/>
-      <c r="O19" s="92"/>
-      <c r="Q19" s="31" t="s">
+      <c r="D19" s="50"/>
+      <c r="E19" s="51"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="40"/>
+      <c r="K19" s="40"/>
+      <c r="L19" s="40"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="40"/>
+      <c r="O19" s="40"/>
+      <c r="Q19" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="R19" s="43" t="s">
+      <c r="R19" s="49" t="s">
         <v>147</v>
       </c>
-      <c r="S19" s="39"/>
-      <c r="T19" s="40"/>
+      <c r="S19" s="47"/>
+      <c r="T19" s="48"/>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B20" s="35">
+      <c r="B20" s="34">
         <v>10</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C20" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="87"/>
-      <c r="E20" s="88"/>
-      <c r="I20" s="92"/>
-      <c r="J20" s="92"/>
-      <c r="K20" s="92"/>
-      <c r="L20" s="92"/>
-      <c r="M20" s="92"/>
-      <c r="N20" s="92"/>
-      <c r="O20" s="92"/>
-      <c r="Q20" s="31" t="s">
+      <c r="D20" s="50"/>
+      <c r="E20" s="51"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="40"/>
+      <c r="M20" s="40"/>
+      <c r="N20" s="40"/>
+      <c r="O20" s="40"/>
+      <c r="Q20" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="R20" s="43" t="s">
+      <c r="R20" s="49" t="s">
         <v>148</v>
       </c>
-      <c r="S20" s="39"/>
-      <c r="T20" s="40"/>
+      <c r="S20" s="47"/>
+      <c r="T20" s="48"/>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B21" s="35"/>
-      <c r="C21" s="43" t="s">
+      <c r="B21" s="34"/>
+      <c r="C21" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="87"/>
-      <c r="E21" s="88"/>
-      <c r="I21" s="92"/>
-      <c r="J21" s="92"/>
-      <c r="K21" s="92"/>
-      <c r="L21" s="92"/>
-      <c r="M21" s="92"/>
-      <c r="N21" s="92"/>
-      <c r="O21" s="92"/>
-      <c r="Q21" s="35" t="s">
+      <c r="D21" s="50"/>
+      <c r="E21" s="51"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="40"/>
+      <c r="O21" s="40"/>
+      <c r="Q21" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="R21" s="43" t="s">
+      <c r="R21" s="49" t="s">
         <v>149</v>
       </c>
-      <c r="S21" s="39"/>
-      <c r="T21" s="40"/>
+      <c r="S21" s="47"/>
+      <c r="T21" s="48"/>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B22" s="35"/>
-      <c r="C22" s="43" t="s">
+      <c r="B22" s="34"/>
+      <c r="C22" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="87"/>
-      <c r="E22" s="88"/>
-      <c r="I22" s="92"/>
-      <c r="J22" s="92"/>
-      <c r="K22" s="92"/>
-      <c r="L22" s="92"/>
-      <c r="M22" s="92"/>
-      <c r="N22" s="92"/>
-      <c r="O22" s="92"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="51"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="40"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="40"/>
+      <c r="M22" s="40"/>
+      <c r="N22" s="40"/>
+      <c r="O22" s="40"/>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B23" s="35">
+      <c r="B23" s="34">
         <v>11</v>
       </c>
-      <c r="C23" s="43" t="s">
+      <c r="C23" s="49" t="s">
         <v>137</v>
       </c>
-      <c r="D23" s="87"/>
-      <c r="E23" s="88"/>
-      <c r="I23" s="92"/>
-      <c r="J23" s="92"/>
-      <c r="K23" s="92"/>
-      <c r="L23" s="92"/>
-      <c r="M23" s="92"/>
-      <c r="N23" s="92"/>
-      <c r="O23" s="92"/>
-      <c r="P23" s="37"/>
-      <c r="Q23" s="37"/>
-      <c r="R23" s="37"/>
-      <c r="S23" s="37"/>
-      <c r="T23" s="37"/>
-    </row>
-    <row r="24" spans="2:20" s="37" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="35"/>
-      <c r="C24" s="91" t="s">
+      <c r="D23" s="50"/>
+      <c r="E23" s="51"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="40"/>
+      <c r="K23" s="40"/>
+      <c r="L23" s="40"/>
+      <c r="M23" s="40"/>
+      <c r="N23" s="40"/>
+      <c r="O23" s="40"/>
+      <c r="P23" s="36"/>
+      <c r="Q23" s="36"/>
+      <c r="R23" s="36"/>
+      <c r="S23" s="36"/>
+      <c r="T23" s="36"/>
+    </row>
+    <row r="24" spans="2:20" s="36" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="34"/>
+      <c r="C24" s="52" t="s">
         <v>136</v>
       </c>
-      <c r="D24" s="87"/>
-      <c r="E24" s="88"/>
-      <c r="I24" s="92"/>
-      <c r="J24" s="92"/>
-      <c r="K24" s="92"/>
-      <c r="L24" s="92"/>
-      <c r="M24" s="92"/>
-      <c r="N24" s="92"/>
-      <c r="O24" s="92"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="51"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="40"/>
+      <c r="M24" s="40"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="40"/>
       <c r="P24"/>
       <c r="Q24"/>
       <c r="R24"/>
@@ -2459,44 +2487,44 @@
       <c r="T24"/>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B25" s="35">
+      <c r="B25" s="34">
         <v>12</v>
       </c>
-      <c r="C25" s="43" t="s">
+      <c r="C25" s="49" t="s">
         <v>139</v>
       </c>
-      <c r="D25" s="87"/>
-      <c r="E25" s="88"/>
-      <c r="I25" s="92"/>
-      <c r="J25" s="92"/>
-      <c r="K25" s="92"/>
-      <c r="L25" s="92"/>
-      <c r="M25" s="92"/>
-      <c r="N25" s="92"/>
-      <c r="O25" s="92"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="51"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="40"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="40"/>
+      <c r="M25" s="40"/>
+      <c r="N25" s="40"/>
+      <c r="O25" s="40"/>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B26" s="35">
+      <c r="B26" s="34">
         <v>13</v>
       </c>
-      <c r="C26" s="43" t="s">
+      <c r="C26" s="49" t="s">
         <v>138</v>
       </c>
-      <c r="D26" s="87"/>
-      <c r="E26" s="88"/>
-      <c r="P26" s="37"/>
-      <c r="Q26" s="37"/>
-      <c r="R26" s="37"/>
-      <c r="S26" s="37"/>
-      <c r="T26" s="37"/>
-    </row>
-    <row r="27" spans="2:20" s="37" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="35"/>
-      <c r="C27" s="36" t="s">
+      <c r="D26" s="50"/>
+      <c r="E26" s="51"/>
+      <c r="P26" s="36"/>
+      <c r="Q26" s="36"/>
+      <c r="R26" s="36"/>
+      <c r="S26" s="36"/>
+      <c r="T26" s="36"/>
+    </row>
+    <row r="27" spans="2:20" s="36" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="34"/>
+      <c r="C27" s="35" t="s">
         <v>140</v>
       </c>
-      <c r="D27" s="89"/>
-      <c r="E27" s="90"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="39"/>
       <c r="P27"/>
       <c r="Q27"/>
       <c r="R27"/>
@@ -2504,60 +2532,39 @@
       <c r="T27"/>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B28" s="35">
+      <c r="B28" s="34">
         <v>6</v>
       </c>
-      <c r="C28" s="43" t="s">
+      <c r="C28" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="D28" s="87"/>
-      <c r="E28" s="88"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="51"/>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B29" s="35">
+      <c r="B29" s="34">
         <v>14</v>
       </c>
-      <c r="C29" s="43" t="s">
+      <c r="C29" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="87"/>
-      <c r="E29" s="88"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="51"/>
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B31" s="92" t="s">
+      <c r="B31" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="C31" s="92"/>
-      <c r="D31" s="92"/>
-      <c r="E31" s="92"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="37"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="R21:T21"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="I6:O6"/>
-    <mergeCell ref="R18:T18"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="R20:T20"/>
+    <mergeCell ref="R19:T19"/>
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="R17:T17"/>
@@ -2570,8 +2577,29 @@
     <mergeCell ref="Q10:S10"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="C9:E9"/>
-    <mergeCell ref="R20:T20"/>
-    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="I6:O6"/>
+    <mergeCell ref="R18:T18"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="R21:T21"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C24:E24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2601,7 +2629,7 @@
     <col min="13" max="13" width="5" customWidth="1"/>
     <col min="15" max="15" width="11.88671875" customWidth="1"/>
     <col min="16" max="17" width="8.88671875" customWidth="1"/>
-    <col min="21" max="21" width="8.88671875" style="37"/>
+    <col min="21" max="21" width="8.88671875" style="36"/>
     <col min="22" max="22" width="9.109375" customWidth="1"/>
     <col min="23" max="25" width="2.109375" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="4.88671875" customWidth="1"/>
@@ -2611,1069 +2639,1069 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B1" s="12"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="11"/>
+      <c r="D1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="40"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="48"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="76" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="40"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="48"/>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B5" s="11"/>
+      <c r="B5" s="10"/>
     </row>
     <row r="6" spans="1:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="39"/>
-      <c r="S6" s="39"/>
-      <c r="T6" s="39"/>
-      <c r="U6" s="39"/>
-      <c r="V6" s="39"/>
-      <c r="W6" s="39"/>
-      <c r="X6" s="39"/>
-      <c r="Y6" s="39"/>
-      <c r="Z6" s="39"/>
-      <c r="AA6" s="39"/>
-      <c r="AB6" s="39"/>
-      <c r="AC6" s="40"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="47"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="47"/>
+      <c r="Q6" s="47"/>
+      <c r="R6" s="47"/>
+      <c r="S6" s="47"/>
+      <c r="T6" s="47"/>
+      <c r="U6" s="47"/>
+      <c r="V6" s="47"/>
+      <c r="W6" s="47"/>
+      <c r="X6" s="47"/>
+      <c r="Y6" s="47"/>
+      <c r="Z6" s="47"/>
+      <c r="AA6" s="47"/>
+      <c r="AB6" s="47"/>
+      <c r="AC6" s="48"/>
     </row>
     <row r="7" spans="1:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="54"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="53" t="s">
+      <c r="B7" s="66"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="77" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="51" t="s">
+      <c r="F7" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="49" t="s">
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="47"/>
+      <c r="K7" s="47"/>
+      <c r="L7" s="47"/>
+      <c r="M7" s="47"/>
+      <c r="N7" s="47"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
-      <c r="T7" s="39"/>
-      <c r="U7" s="39"/>
-      <c r="V7" s="40"/>
-      <c r="W7" s="106" t="s">
+      <c r="Q7" s="47"/>
+      <c r="R7" s="47"/>
+      <c r="S7" s="47"/>
+      <c r="T7" s="47"/>
+      <c r="U7" s="47"/>
+      <c r="V7" s="48"/>
+      <c r="W7" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="X7" s="107"/>
-      <c r="Y7" s="107"/>
-      <c r="Z7" s="107"/>
-      <c r="AA7" s="107"/>
-      <c r="AB7" s="107"/>
-      <c r="AC7" s="105"/>
+      <c r="X7" s="72"/>
+      <c r="Y7" s="72"/>
+      <c r="Z7" s="72"/>
+      <c r="AA7" s="72"/>
+      <c r="AB7" s="72"/>
+      <c r="AC7" s="45"/>
     </row>
     <row r="8" spans="1:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="54"/>
-      <c r="C8" s="52" t="s">
+      <c r="B8" s="66"/>
+      <c r="C8" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="52" t="s">
+      <c r="D8" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="54"/>
-      <c r="F8" s="51" t="s">
+      <c r="E8" s="66"/>
+      <c r="F8" s="74" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="40"/>
-      <c r="H8" s="51" t="s">
+      <c r="G8" s="48"/>
+      <c r="H8" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="I8" s="40"/>
-      <c r="J8" s="51" t="s">
+      <c r="I8" s="48"/>
+      <c r="J8" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="K8" s="40"/>
-      <c r="L8" s="51" t="s">
+      <c r="K8" s="48"/>
+      <c r="L8" s="74" t="s">
         <v>55</v>
       </c>
-      <c r="M8" s="40"/>
-      <c r="N8" s="51" t="s">
+      <c r="M8" s="48"/>
+      <c r="N8" s="74" t="s">
         <v>56</v>
       </c>
-      <c r="O8" s="40"/>
-      <c r="P8" s="49" t="s">
+      <c r="O8" s="48"/>
+      <c r="P8" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="Q8" s="49" t="s">
+      <c r="Q8" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="R8" s="49" t="s">
+      <c r="R8" s="73" t="s">
         <v>59</v>
       </c>
-      <c r="S8" s="49" t="s">
+      <c r="S8" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="T8" s="99" t="s">
+      <c r="T8" s="69" t="s">
         <v>169</v>
       </c>
-      <c r="U8" s="49" t="s">
+      <c r="U8" s="73" t="s">
         <v>170</v>
       </c>
-      <c r="V8" s="47">
+      <c r="V8" s="68">
         <v>0</v>
       </c>
-      <c r="W8" s="47">
+      <c r="W8" s="68">
         <v>1</v>
       </c>
-      <c r="X8" s="47">
+      <c r="X8" s="68">
         <v>2</v>
       </c>
-      <c r="Y8" s="47" t="s">
+      <c r="Y8" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="Z8" s="47" t="s">
+      <c r="Z8" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="AA8" s="47" t="s">
+      <c r="AA8" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="AB8" s="47" t="s">
+      <c r="AB8" s="68" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="13" t="s">
+      <c r="B9" s="67"/>
+      <c r="C9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="J9" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="K9" s="13" t="s">
+      <c r="K9" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="L9" s="13" t="s">
+      <c r="L9" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="M9" s="13" t="s">
+      <c r="M9" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="N9" s="13" t="s">
+      <c r="N9" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="O9" s="13" t="s">
+      <c r="O9" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="P9" s="48"/>
-      <c r="Q9" s="48"/>
-      <c r="R9" s="48"/>
-      <c r="S9" s="48"/>
-      <c r="T9" s="100"/>
-      <c r="U9" s="48"/>
-      <c r="V9" s="48"/>
-      <c r="W9" s="48"/>
-      <c r="X9" s="48"/>
-      <c r="Y9" s="48"/>
-      <c r="Z9" s="48"/>
-      <c r="AA9" s="48"/>
-      <c r="AB9" s="48"/>
+      <c r="P9" s="67"/>
+      <c r="Q9" s="67"/>
+      <c r="R9" s="67"/>
+      <c r="S9" s="67"/>
+      <c r="T9" s="70"/>
+      <c r="U9" s="67"/>
+      <c r="V9" s="67"/>
+      <c r="W9" s="67"/>
+      <c r="X9" s="67"/>
+      <c r="Y9" s="67"/>
+      <c r="Z9" s="67"/>
+      <c r="AA9" s="67"/>
+      <c r="AB9" s="67"/>
     </row>
     <row r="10" spans="1:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="37"/>
-      <c r="B10" s="14" t="s">
+      <c r="A10" s="36"/>
+      <c r="B10" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="K10" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="L10" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="M10" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="N10" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="O10" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="P10" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q10" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="R10" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="S10" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="T10" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="U10" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="V10" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="W10" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="X10" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y10" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z10" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA10" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB10" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC10" s="37"/>
+      <c r="F10" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="O10" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="P10" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q10" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="R10" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="S10" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="T10" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="U10" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="V10" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="W10" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="X10" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y10" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z10" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA10" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB10" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC10" s="36"/>
     </row>
     <row r="11" spans="1:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="37"/>
-      <c r="B11" s="14" t="s">
+      <c r="A11" s="36"/>
+      <c r="B11" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="F11" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="I11" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="J11" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="K11" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="L11" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="M11" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="O11" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="P11" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q11" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="R11" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="S11" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="T11" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="U11" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="V11" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="W11" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="X11" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y11" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z11" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA11" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB11" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC11" s="37"/>
+      <c r="F11" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="N11" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="O11" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="P11" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q11" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="R11" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="S11" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="T11" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="U11" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="V11" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="W11" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="X11" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y11" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z11" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA11" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB11" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC11" s="36"/>
     </row>
     <row r="12" spans="1:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="37"/>
-      <c r="B12" s="14" t="s">
+      <c r="A12" s="36"/>
+      <c r="B12" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="97" t="s">
+      <c r="C12" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="98" t="s">
+      <c r="D12" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="F12" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="I12" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J12" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="K12" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="L12" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="M12" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="O12" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="P12" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q12" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="R12" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="S12" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="T12" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="U12" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="V12" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="W12" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="X12" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y12" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z12" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA12" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB12" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC12" s="37"/>
+      <c r="F12" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="N12" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="O12" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="P12" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q12" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="R12" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="S12" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="T12" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="U12" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="V12" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="W12" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="X12" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y12" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z12" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA12" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB12" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC12" s="36"/>
     </row>
     <row r="13" spans="1:29" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="37"/>
-      <c r="B13" s="14" t="s">
+      <c r="A13" s="36"/>
+      <c r="B13" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="F13" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="H13" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="I13" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J13" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="K13" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="L13" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="M13" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="O13" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="P13" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q13" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="R13" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="S13" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="T13" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="U13" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="V13" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="W13" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="X13" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y13" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z13" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA13" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB13" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC13" s="37"/>
+      <c r="F13" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="N13" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="O13" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="P13" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q13" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="R13" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="S13" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="T13" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="U13" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="V13" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="W13" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="X13" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y13" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z13" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA13" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB13" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC13" s="36"/>
     </row>
     <row r="14" spans="1:29" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="37"/>
-      <c r="B14" s="14" t="s">
+      <c r="A14" s="36"/>
+      <c r="B14" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="F14" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="I14" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J14" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="K14" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="L14" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="M14" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="N14" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="O14" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="P14" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q14" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="R14" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="S14" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="T14" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="U14" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="V14" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="W14" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="X14" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y14" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z14" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA14" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB14" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC14" s="37"/>
+      <c r="F14" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N14" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="O14" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="P14" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q14" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="R14" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="S14" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="T14" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="U14" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="V14" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="W14" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="X14" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y14" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z14" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA14" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB14" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC14" s="36"/>
     </row>
     <row r="15" spans="1:29" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="37"/>
-      <c r="B15" s="14" t="s">
+      <c r="A15" s="36"/>
+      <c r="B15" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="F15" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="G15" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="H15" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="I15" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J15" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="K15" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="L15" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="M15" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="N15" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="O15" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="P15" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q15" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="R15" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="S15" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="T15" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="U15" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="V15" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="W15" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="X15" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y15" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z15" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA15" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB15" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC15" s="37"/>
+      <c r="F15" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N15" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="O15" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="P15" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q15" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="R15" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="S15" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="T15" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="U15" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="V15" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="W15" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="X15" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y15" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z15" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA15" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB15" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC15" s="36"/>
     </row>
     <row r="16" spans="1:29" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="37"/>
-      <c r="B16" s="14" t="s">
+      <c r="A16" s="36"/>
+      <c r="B16" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="F16" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="I16" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J16" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="K16" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="L16" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="M16" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="O16" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="P16" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q16" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="R16" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="S16" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="T16" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="U16" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="V16" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="W16" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="X16" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y16" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z16" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA16" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB16" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC16" s="37"/>
+      <c r="F16" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N16" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="O16" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="P16" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q16" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="R16" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="S16" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="T16" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="U16" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="V16" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="W16" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="X16" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y16" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z16" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA16" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB16" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC16" s="36"/>
     </row>
     <row r="17" spans="1:29" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
-      <c r="B17" s="14" t="s">
+      <c r="A17" s="36"/>
+      <c r="B17" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="F17" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="H17" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="I17" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J17" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="K17" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="L17" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="M17" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="O17" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="P17" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q17" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="R17" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="S17" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="T17" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="U17" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="V17" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="W17" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="X17" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y17" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z17" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA17" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB17" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC17" s="37"/>
+      <c r="F17" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J17" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N17" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="O17" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="P17" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q17" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="R17" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="S17" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="T17" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="U17" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="V17" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="W17" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="X17" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y17" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z17" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA17" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB17" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC17" s="36"/>
     </row>
     <row r="18" spans="1:29" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="37"/>
-      <c r="B18" s="14" t="s">
+      <c r="A18" s="36"/>
+      <c r="B18" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="F18" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="H18" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="I18" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J18" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="K18" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="L18" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="M18" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="O18" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="P18" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q18" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="R18" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="S18" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="T18" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="U18" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="V18" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="W18" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="X18" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y18" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z18" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA18" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB18" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC18" s="37"/>
+      <c r="F18" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J18" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N18" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="O18" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="P18" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q18" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="R18" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="S18" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="T18" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="U18" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="V18" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="W18" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="X18" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y18" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z18" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA18" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB18" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC18" s="36"/>
     </row>
     <row r="19" spans="1:29" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="37"/>
-      <c r="B19" s="14" t="s">
+      <c r="A19" s="36"/>
+      <c r="B19" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="F19" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="H19" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J19" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="K19" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="L19" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="M19" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="O19" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="P19" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q19" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="R19" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="S19" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="T19" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="U19" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="V19" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="W19" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="X19" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y19" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z19" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA19" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB19" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC19" s="37"/>
+      <c r="F19" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J19" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="N19" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="O19" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="P19" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q19" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="R19" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="S19" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="T19" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="U19" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="V19" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="W19" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="X19" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y19" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z19" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA19" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB19" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC19" s="36"/>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -3681,143 +3709,138 @@
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A23" s="37" t="s">
+      <c r="A23" s="36" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A24" s="37" t="s">
+      <c r="A24" s="36" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
+      <c r="A25" s="36"/>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="36" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="36" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A28" s="37" t="s">
+      <c r="A28" s="36" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A29" s="37"/>
+      <c r="A29" s="36"/>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A30" s="37" t="s">
+      <c r="A30" s="36" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A31" s="37" t="s">
+      <c r="A31" s="36" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A32" s="37"/>
+      <c r="A32" s="36"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="37"/>
+      <c r="A33" s="36"/>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="37" t="s">
+      <c r="A34" s="36" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="37" t="s">
+      <c r="A35" s="36" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="37" t="s">
+      <c r="A36" s="36" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="37"/>
+      <c r="A37" s="36"/>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="37" t="s">
+      <c r="A38" s="36" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="37"/>
+      <c r="A39" s="36"/>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="37"/>
+      <c r="A40" s="36"/>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="37"/>
+      <c r="A41" s="36"/>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="37"/>
+      <c r="A42" s="36"/>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="37" t="s">
+      <c r="A43" s="36" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="37" t="s">
+      <c r="A44" s="36" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="37"/>
+      <c r="A45" s="36"/>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="37" t="s">
+      <c r="A46" s="36" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="37" t="s">
+      <c r="A47" s="36" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="37"/>
+      <c r="A48" s="36"/>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="37"/>
+      <c r="A49" s="36"/>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="37" t="s">
+      <c r="A50" s="36" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="37"/>
+      <c r="A51" s="36"/>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="37"/>
+      <c r="A52" s="36"/>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="37"/>
+      <c r="A53" s="36"/>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="37"/>
+      <c r="A54" s="36"/>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="37"/>
+      <c r="A55" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="W7:AB7"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="S8:S9"/>
     <mergeCell ref="L8:M8"/>
@@ -3834,6 +3857,11 @@
     <mergeCell ref="P8:P9"/>
     <mergeCell ref="AB8:AB9"/>
     <mergeCell ref="V8:V9"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="W7:AB7"/>
     <mergeCell ref="R8:R9"/>
     <mergeCell ref="X8:X9"/>
     <mergeCell ref="C6:C7"/>
@@ -3855,7 +3883,7 @@
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B1:N16"/>
+  <dimension ref="B1:N21"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
@@ -3871,49 +3899,49 @@
     <col min="15" max="15" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B1" s="12"/>
-      <c r="D1" s="38" t="s">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B1" s="11"/>
+      <c r="D1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="40"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="110" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="48"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="94" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="111"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="111"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="112"/>
-    </row>
-    <row r="4" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="80" t="s">
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="96"/>
+    </row>
+    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="76" t="s">
+      <c r="C4" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="58" t="s">
+      <c r="D4" s="98" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="108" t="s">
+      <c r="E4" s="78" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="109"/>
-      <c r="G4" s="57" t="s">
+      <c r="F4" s="79"/>
+      <c r="G4" s="82" t="s">
         <v>98</v>
       </c>
-      <c r="H4" s="40"/>
-    </row>
-    <row r="5" spans="2:14" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="81"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="59"/>
+      <c r="H4" s="48"/>
+    </row>
+    <row r="5" spans="2:12" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="90"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="99"/>
       <c r="E5" s="2" t="s">
         <v>99</v>
       </c>
@@ -3927,284 +3955,392 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="20">
+    <row r="6" spans="2:12" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="19">
         <v>1</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="112" t="s">
         <v>103</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F6" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="G6" s="21" t="s">
+      <c r="F6" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="20" t="s">
+      <c r="H6" s="19" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="20">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="19">
         <v>2</v>
       </c>
-      <c r="C7" s="61"/>
+      <c r="C7" s="113"/>
       <c r="D7" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="F7" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="G7" s="20" t="s">
+      <c r="F7" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="19" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B8" s="20">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="19">
         <v>3</v>
       </c>
-      <c r="C8" s="61"/>
-      <c r="D8" s="10" t="s">
+      <c r="C8" s="113"/>
+      <c r="D8" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="19" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B9" s="20">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="19">
         <v>4</v>
       </c>
-      <c r="C9" s="61"/>
-      <c r="D9" s="10" t="s">
+      <c r="C9" s="113"/>
+      <c r="D9" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="G9" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="H9" s="20" t="s">
+      <c r="H9" s="19" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="2">
+    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="37">
         <v>5</v>
       </c>
-      <c r="C10" s="62"/>
-      <c r="D10" s="9" t="s">
+      <c r="C10" s="113"/>
+      <c r="D10" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="37" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="2:14" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="3" t="s">
+    <row r="11" spans="2:12" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="20">
+        <v>6</v>
+      </c>
+      <c r="C11" s="113"/>
+      <c r="D11" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="F11" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="20">
+        <v>7</v>
+      </c>
+      <c r="C12" s="113"/>
+      <c r="D12" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>177</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="G12" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="20">
+        <v>8</v>
+      </c>
+      <c r="C13" s="113"/>
+      <c r="D13" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="F13" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="G13" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" s="37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="20">
+        <v>9</v>
+      </c>
+      <c r="C14" s="113"/>
+      <c r="D14" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="G14" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="20">
+        <v>10</v>
+      </c>
+      <c r="C15" s="113"/>
+      <c r="D15" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="F15" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="G15" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="114" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="2:12" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="111"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="K12" s="22"/>
-    </row>
-    <row r="13" spans="2:14" ht="15.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="82" t="s">
+      <c r="K17" s="21"/>
+    </row>
+    <row r="18" spans="2:14" ht="15.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="91" t="s">
         <v>112</v>
       </c>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="71" t="s">
+      <c r="C18" s="92"/>
+      <c r="D18" s="92"/>
+      <c r="E18" s="92"/>
+      <c r="F18" s="107" t="s">
         <v>113</v>
       </c>
-      <c r="G13" s="66"/>
-      <c r="H13" s="72" t="s">
+      <c r="G18" s="103"/>
+      <c r="H18" s="108" t="s">
         <v>114</v>
       </c>
-      <c r="I13" s="73"/>
-      <c r="J13" s="73"/>
-      <c r="K13" s="73"/>
-      <c r="L13" s="74"/>
-      <c r="M13" s="65" t="s">
+      <c r="I18" s="92"/>
+      <c r="J18" s="92"/>
+      <c r="K18" s="92"/>
+      <c r="L18" s="109"/>
+      <c r="M18" s="102" t="s">
         <v>115</v>
       </c>
-      <c r="N13" s="66"/>
-    </row>
-    <row r="14" spans="2:14" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="77" t="s">
+      <c r="N18" s="103"/>
+    </row>
+    <row r="19" spans="2:14" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="83" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="67" t="s">
+      <c r="C19" s="88" t="s">
         <v>117</v>
       </c>
-      <c r="D14" s="67" t="s">
+      <c r="D19" s="88" t="s">
         <v>118</v>
       </c>
-      <c r="E14" s="83" t="s">
+      <c r="E19" s="93" t="s">
         <v>119</v>
       </c>
-      <c r="F14" s="75" t="s">
+      <c r="F19" s="110" t="s">
         <v>120</v>
       </c>
-      <c r="G14" s="63" t="s">
+      <c r="G19" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="H14" s="79" t="s">
+      <c r="H19" s="87" t="s">
         <v>122</v>
       </c>
-      <c r="I14" s="67" t="s">
+      <c r="I19" s="88" t="s">
         <v>116</v>
       </c>
-      <c r="J14" s="67" t="s">
+      <c r="J19" s="88" t="s">
         <v>117</v>
       </c>
-      <c r="K14" s="68" t="s">
+      <c r="K19" s="104" t="s">
         <v>123</v>
       </c>
-      <c r="L14" s="78" t="s">
+      <c r="L19" s="85" t="s">
         <v>124</v>
       </c>
-      <c r="M14" s="69" t="s">
+      <c r="M19" s="106" t="s">
         <v>125</v>
       </c>
-      <c r="N14" s="55" t="s">
+      <c r="N19" s="97" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B15" s="70"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="70"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="44"/>
-      <c r="L15" s="56"/>
-      <c r="M15" s="70"/>
-      <c r="N15" s="56"/>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B16" s="26">
-        <f>SUM(C16:D16)</f>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B20" s="84"/>
+      <c r="C20" s="67"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="86"/>
+      <c r="G20" s="101"/>
+      <c r="H20" s="84"/>
+      <c r="I20" s="67"/>
+      <c r="J20" s="67"/>
+      <c r="K20" s="105"/>
+      <c r="L20" s="86"/>
+      <c r="M20" s="84"/>
+      <c r="N20" s="86"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B21" s="25">
+        <f>SUM(C21:D21)</f>
         <v>10</v>
       </c>
-      <c r="C16" s="23">
+      <c r="C21" s="22">
         <v>10</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D21" s="22">
         <v>0</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E21" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F21" s="24">
         <v>0</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G21" s="8">
         <v>0</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H21" s="7">
         <v>0</v>
       </c>
-      <c r="I16" s="26">
-        <f>SUM(J16:K16)</f>
+      <c r="I21" s="25">
+        <f>SUM(J21:K21)</f>
         <v>10</v>
       </c>
-      <c r="J16" s="23">
+      <c r="J21" s="22">
         <v>10</v>
       </c>
-      <c r="K16" s="27">
+      <c r="K21" s="26">
         <v>0</v>
       </c>
-      <c r="L16" s="28" t="s">
+      <c r="L21" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="M16" s="6" t="s">
+      <c r="M21" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="N16" s="29">
-        <f>C16</f>
+      <c r="N21" s="28">
+        <f>C21</f>
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:L18"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="C6:C15"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="J19:J20"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="C6:C10"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="E19:E20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
+++ b/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alle\IdeaProjects\VVSS\docs\Lab03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UBB an 3 sem 2\VVSS\docs\Lab03\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5CBF97A-5138-4D66-B806-AF475DE7717C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45648" yWindow="1476" windowWidth="28800" windowHeight="15348" activeTab="3"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -17,12 +18,25 @@
     <sheet name="F02.TCs" sheetId="3" r:id="rId3"/>
     <sheet name="WBT-TCs" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="210">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -405,9 +419,6 @@
     <t>#TCs passed [de executat in testarea de regresie]</t>
   </si>
   <si>
-    <t>51%</t>
-  </si>
-  <si>
     <t>da</t>
   </si>
   <si>
@@ -574,13 +585,94 @@
   </si>
   <si>
     <t>Reteta(1,[{apa,-5.0}])</t>
+  </si>
+  <si>
+    <t>F02_TC11</t>
+  </si>
+  <si>
+    <t>F02_TC12</t>
+  </si>
+  <si>
+    <t>stocList.size=1</t>
+  </si>
+  <si>
+    <t>F02_TC13</t>
+  </si>
+  <si>
+    <t>F02_TC14</t>
+  </si>
+  <si>
+    <t>stocList=[]</t>
+  </si>
+  <si>
+    <t>F02_TC15</t>
+  </si>
+  <si>
+    <t>throws ISE</t>
+  </si>
+  <si>
+    <t>F02_TC16</t>
+  </si>
+  <si>
+    <t>F02_TC17</t>
+  </si>
+  <si>
+    <t>F02_TC18</t>
+  </si>
+  <si>
+    <t>stoc: [cafea=10.0]</t>
+  </si>
+  <si>
+    <t>lista.size=1, "cafea"</t>
+  </si>
+  <si>
+    <t>stocList[0].cantitate=30.0</t>
+  </si>
+  <si>
+    <t>Reteta(1, [{apa,100.0}])</t>
+  </si>
+  <si>
+    <t>stoc: [apa=20.0]</t>
+  </si>
+  <si>
+    <t>Reteta(1, [{zahar,60.0}])</t>
+  </si>
+  <si>
+    <t>stoc: [zahar=100.0, zahar=50.0]</t>
+  </si>
+  <si>
+    <t>stoc: [zahar=40.0, zahar=50.0]</t>
+  </si>
+  <si>
+    <t>Reteta(1, [{apa,80.0}])</t>
+  </si>
+  <si>
+    <t>stoc: [apa=50.0, apa=50.0]</t>
+  </si>
+  <si>
+    <t>stoc: [apa=0.0, apa=20.0]</t>
+  </si>
+  <si>
+    <t>Reteta(1, [{apa,0.0}])</t>
+  </si>
+  <si>
+    <t>stoc: [apa=100.0]</t>
+  </si>
+  <si>
+    <t>stoc: [lapte=50.0]</t>
+  </si>
+  <si>
+    <t>stoc: [sirop=30.0]</t>
+  </si>
+  <si>
+    <t>stoc: [cacao=10.0]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="13" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -677,6 +769,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -1189,7 +1287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1243,11 +1341,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1261,14 +1357,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1276,8 +1365,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1289,94 +1377,65 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1394,15 +1453,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1412,63 +1466,87 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1503,7 +1581,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1541,7 +1625,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1584,7 +1674,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1597,8 +1693,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="647700" y="4264727"/>
-          <a:ext cx="5691864" cy="5466013"/>
+          <a:off x="647700" y="5684224"/>
+          <a:ext cx="5707296" cy="5529151"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1611,9 +1707,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1651,9 +1747,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1688,7 +1784,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1723,7 +1819,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1896,7 +1992,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
@@ -1908,15 +2004,15 @@
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B1" s="11"/>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="49"/>
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="31" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1934,21 +2030,21 @@
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N5" s="30" t="s">
+      <c r="N5" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="O5" s="30"/>
-      <c r="P5" s="30"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25" t="s">
+      <c r="N6" s="24"/>
+      <c r="O6" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="P6" s="25" t="s">
+      <c r="P6" s="24" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1957,13 +2053,13 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="N7" s="25" t="s">
+      <c r="N7" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="O7" s="25" t="s">
+      <c r="O7" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="P7" s="25">
+      <c r="P7" s="24">
         <v>234</v>
       </c>
     </row>
@@ -1972,13 +2068,13 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="N8" s="25" t="s">
+      <c r="N8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="O8" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="P8" s="25">
+      <c r="O8" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="P8" s="24">
         <v>234</v>
       </c>
     </row>
@@ -1989,13 +2085,13 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="N9" s="25" t="s">
+      <c r="N9" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="O9" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="P9" s="25">
+      <c r="O9" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="P9" s="24">
         <v>234</v>
       </c>
     </row>
@@ -2008,7 +2104,7 @@
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="30" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="1"/>
@@ -2036,7 +2132,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
@@ -2053,521 +2149,371 @@
   <sheetData>
     <row r="1" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B1" s="11"/>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="49"/>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="63"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="82"/>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="I6" s="53" t="s">
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="49"/>
+      <c r="I6" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="47"/>
-      <c r="K6" s="47"/>
-      <c r="L6" s="47"/>
-      <c r="M6" s="47"/>
-      <c r="N6" s="47"/>
-      <c r="O6" s="47"/>
-      <c r="Q6" s="53" t="s">
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="48"/>
+      <c r="Q6" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="R6" s="47"/>
-      <c r="S6" s="47"/>
-      <c r="T6" s="47"/>
-    </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="48"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B8" s="41">
+      <c r="B8" s="35">
         <v>1</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="59"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="84"/>
       <c r="I8" s="11"/>
-      <c r="Q8" s="57" t="s">
+      <c r="Q8" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="R8" s="47"/>
-      <c r="S8" s="48"/>
-      <c r="T8" s="29">
+      <c r="R8" s="48"/>
+      <c r="S8" s="49"/>
+      <c r="T8" s="27">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B9" s="30">
+      <c r="B9" s="28">
         <v>2</v>
       </c>
-      <c r="C9" s="49" t="s">
+      <c r="C9" s="79" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" s="83"/>
+      <c r="E9" s="84"/>
+      <c r="Q9" s="85" t="s">
+        <v>22</v>
+      </c>
+      <c r="R9" s="48"/>
+      <c r="S9" s="49"/>
+      <c r="T9" s="27" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B10" s="28">
+        <v>3</v>
+      </c>
+      <c r="C10" s="87" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="48"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="Q10" s="85" t="s">
+        <v>24</v>
+      </c>
+      <c r="R10" s="48"/>
+      <c r="S10" s="49"/>
+      <c r="T10" s="27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B11" s="28"/>
+      <c r="C11" s="79" t="s">
         <v>131</v>
       </c>
-      <c r="D9" s="50"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="Q9" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="R9" s="47"/>
-      <c r="S9" s="48"/>
-      <c r="T9" s="29" t="s">
+      <c r="D11" s="83"/>
+      <c r="E11" s="84"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B12" s="28">
+        <v>4</v>
+      </c>
+      <c r="C12" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="83"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B13" s="28">
+        <v>5</v>
+      </c>
+      <c r="C13" s="79" t="s">
+        <v>132</v>
+      </c>
+      <c r="D13" s="83"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="Q13" s="86" t="s">
+        <v>28</v>
+      </c>
+      <c r="R13" s="48"/>
+      <c r="S13" s="48"/>
+      <c r="T13" s="48"/>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B14" s="28">
+        <v>6</v>
+      </c>
+      <c r="C14" s="79" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="83"/>
+      <c r="E14" s="84"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B15" s="28"/>
+      <c r="C15" s="79" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="83"/>
+      <c r="E15" s="84"/>
+      <c r="Q15" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="R15" s="79" t="s">
+        <v>144</v>
+      </c>
+      <c r="S15" s="48"/>
+      <c r="T15" s="49"/>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B16" s="28">
+        <v>7</v>
+      </c>
+      <c r="C16" s="79" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="83"/>
+      <c r="E16" s="84"/>
+      <c r="Q16" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="R16" s="79" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B10" s="30">
-        <v>3</v>
-      </c>
-      <c r="C10" s="64" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="47"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="40"/>
-      <c r="Q10" s="57" t="s">
-        <v>24</v>
-      </c>
-      <c r="R10" s="47"/>
-      <c r="S10" s="48"/>
-      <c r="T10" s="29" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B11" s="30"/>
-      <c r="C11" s="49" t="s">
-        <v>132</v>
-      </c>
-      <c r="D11" s="50"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="40"/>
-      <c r="N11" s="40"/>
-      <c r="O11" s="40"/>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B12" s="30">
-        <v>4</v>
-      </c>
-      <c r="C12" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="50"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="40"/>
-      <c r="M12" s="40"/>
-      <c r="N12" s="40"/>
-      <c r="O12" s="40"/>
-    </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B13" s="30">
-        <v>5</v>
-      </c>
-      <c r="C13" s="49" t="s">
-        <v>133</v>
-      </c>
-      <c r="D13" s="50"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="40"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="40"/>
-      <c r="O13" s="40"/>
-      <c r="Q13" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="R13" s="47"/>
-      <c r="S13" s="47"/>
-      <c r="T13" s="47"/>
-    </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B14" s="30">
+      <c r="S16" s="48"/>
+      <c r="T16" s="49"/>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B17" s="28">
         <v>6</v>
       </c>
-      <c r="C14" s="49" t="s">
+      <c r="C17" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="50"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="40"/>
-      <c r="M14" s="40"/>
-      <c r="N14" s="40"/>
-      <c r="O14" s="40"/>
-    </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B15" s="34"/>
-      <c r="C15" s="49" t="s">
+      <c r="D17" s="83"/>
+      <c r="E17" s="84"/>
+      <c r="Q17" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="R17" s="79" t="s">
+        <v>145</v>
+      </c>
+      <c r="S17" s="48"/>
+      <c r="T17" s="49"/>
+    </row>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B18" s="28"/>
+      <c r="C18" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="50"/>
-      <c r="E15" s="51"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="40"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="40"/>
-      <c r="M15" s="40"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="40"/>
-      <c r="Q15" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R15" s="49" t="s">
-        <v>145</v>
-      </c>
-      <c r="S15" s="47"/>
-      <c r="T15" s="48"/>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B16" s="34">
-        <v>7</v>
-      </c>
-      <c r="C16" s="49" t="s">
+      <c r="D18" s="83"/>
+      <c r="E18" s="84"/>
+      <c r="Q18" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="R18" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="S18" s="89"/>
+      <c r="T18" s="90"/>
+    </row>
+    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B19" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="C19" s="79" t="s">
         <v>134</v>
       </c>
-      <c r="D16" s="50"/>
-      <c r="E16" s="51"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="40"/>
-      <c r="M16" s="40"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40"/>
-      <c r="Q16" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="R16" s="49" t="s">
-        <v>144</v>
-      </c>
-      <c r="S16" s="47"/>
-      <c r="T16" s="48"/>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B17" s="34">
+      <c r="D19" s="83"/>
+      <c r="E19" s="84"/>
+      <c r="Q19" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="R19" s="79" t="s">
+        <v>146</v>
+      </c>
+      <c r="S19" s="48"/>
+      <c r="T19" s="49"/>
+    </row>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B20" s="28">
+        <v>10</v>
+      </c>
+      <c r="C20" s="79" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="83"/>
+      <c r="E20" s="84"/>
+      <c r="Q20" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="R20" s="79" t="s">
+        <v>147</v>
+      </c>
+      <c r="S20" s="48"/>
+      <c r="T20" s="49"/>
+    </row>
+    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B21" s="28"/>
+      <c r="C21" s="79" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="83"/>
+      <c r="E21" s="84"/>
+      <c r="Q21" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="R21" s="79" t="s">
+        <v>148</v>
+      </c>
+      <c r="S21" s="48"/>
+      <c r="T21" s="49"/>
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B22" s="28"/>
+      <c r="C22" s="79" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="83"/>
+      <c r="E22" s="84"/>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B23" s="28">
+        <v>11</v>
+      </c>
+      <c r="C23" s="79" t="s">
+        <v>136</v>
+      </c>
+      <c r="D23" s="83"/>
+      <c r="E23" s="84"/>
+    </row>
+    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B24" s="28"/>
+      <c r="C24" s="92" t="s">
+        <v>135</v>
+      </c>
+      <c r="D24" s="83"/>
+      <c r="E24" s="84"/>
+    </row>
+    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B25" s="28">
+        <v>12</v>
+      </c>
+      <c r="C25" s="79" t="s">
+        <v>138</v>
+      </c>
+      <c r="D25" s="83"/>
+      <c r="E25" s="84"/>
+    </row>
+    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B26" s="28">
+        <v>13</v>
+      </c>
+      <c r="C26" s="79" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="83"/>
+      <c r="E26" s="84"/>
+    </row>
+    <row r="27" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B27" s="28"/>
+      <c r="C27" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="D27" s="33"/>
+      <c r="E27" s="34"/>
+    </row>
+    <row r="28" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B28" s="28">
         <v>6</v>
       </c>
-      <c r="C17" s="49" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="50"/>
-      <c r="E17" s="51"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="40"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="40"/>
-      <c r="M17" s="40"/>
-      <c r="N17" s="40"/>
-      <c r="O17" s="40"/>
-      <c r="Q17" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="R17" s="49" t="s">
-        <v>146</v>
-      </c>
-      <c r="S17" s="47"/>
-      <c r="T17" s="48"/>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B18" s="34"/>
-      <c r="C18" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="50"/>
-      <c r="E18" s="51"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="40"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="40"/>
-      <c r="M18" s="40"/>
-      <c r="N18" s="40"/>
-      <c r="O18" s="40"/>
-      <c r="Q18" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="R18" s="54" t="s">
-        <v>174</v>
-      </c>
-      <c r="S18" s="55"/>
-      <c r="T18" s="56"/>
-    </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B19" s="34" t="s">
+      <c r="C28" s="79" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="83"/>
+      <c r="E28" s="84"/>
+    </row>
+    <row r="29" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B29" s="28">
+        <v>14</v>
+      </c>
+      <c r="C29" s="79" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" s="83"/>
+      <c r="E29" s="84"/>
+    </row>
+    <row r="31" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
         <v>141</v>
       </c>
-      <c r="C19" s="49" t="s">
-        <v>135</v>
-      </c>
-      <c r="D19" s="50"/>
-      <c r="E19" s="51"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="40"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="40"/>
-      <c r="M19" s="40"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="40"/>
-      <c r="Q19" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="R19" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="S19" s="47"/>
-      <c r="T19" s="48"/>
-    </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B20" s="34">
-        <v>10</v>
-      </c>
-      <c r="C20" s="49" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="50"/>
-      <c r="E20" s="51"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="40"/>
-      <c r="M20" s="40"/>
-      <c r="N20" s="40"/>
-      <c r="O20" s="40"/>
-      <c r="Q20" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="R20" s="49" t="s">
-        <v>148</v>
-      </c>
-      <c r="S20" s="47"/>
-      <c r="T20" s="48"/>
-    </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B21" s="34"/>
-      <c r="C21" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" s="50"/>
-      <c r="E21" s="51"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="40"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="40"/>
-      <c r="M21" s="40"/>
-      <c r="N21" s="40"/>
-      <c r="O21" s="40"/>
-      <c r="Q21" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="R21" s="49" t="s">
-        <v>149</v>
-      </c>
-      <c r="S21" s="47"/>
-      <c r="T21" s="48"/>
-    </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B22" s="34"/>
-      <c r="C22" s="49" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" s="50"/>
-      <c r="E22" s="51"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="40"/>
-      <c r="M22" s="40"/>
-      <c r="N22" s="40"/>
-      <c r="O22" s="40"/>
-    </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B23" s="34">
-        <v>11</v>
-      </c>
-      <c r="C23" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="D23" s="50"/>
-      <c r="E23" s="51"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="40"/>
-      <c r="K23" s="40"/>
-      <c r="L23" s="40"/>
-      <c r="M23" s="40"/>
-      <c r="N23" s="40"/>
-      <c r="O23" s="40"/>
-      <c r="P23" s="36"/>
-      <c r="Q23" s="36"/>
-      <c r="R23" s="36"/>
-      <c r="S23" s="36"/>
-      <c r="T23" s="36"/>
-    </row>
-    <row r="24" spans="2:20" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="34"/>
-      <c r="C24" s="52" t="s">
-        <v>136</v>
-      </c>
-      <c r="D24" s="50"/>
-      <c r="E24" s="51"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="40"/>
-      <c r="M24" s="40"/>
-      <c r="N24" s="40"/>
-      <c r="O24" s="40"/>
-      <c r="P24"/>
-      <c r="Q24"/>
-      <c r="R24"/>
-      <c r="S24"/>
-      <c r="T24"/>
-    </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B25" s="34">
-        <v>12</v>
-      </c>
-      <c r="C25" s="49" t="s">
-        <v>139</v>
-      </c>
-      <c r="D25" s="50"/>
-      <c r="E25" s="51"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="40"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="40"/>
-      <c r="M25" s="40"/>
-      <c r="N25" s="40"/>
-      <c r="O25" s="40"/>
-    </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B26" s="34">
-        <v>13</v>
-      </c>
-      <c r="C26" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="D26" s="50"/>
-      <c r="E26" s="51"/>
-      <c r="P26" s="36"/>
-      <c r="Q26" s="36"/>
-      <c r="R26" s="36"/>
-      <c r="S26" s="36"/>
-      <c r="T26" s="36"/>
-    </row>
-    <row r="27" spans="2:20" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="34"/>
-      <c r="C27" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="D27" s="38"/>
-      <c r="E27" s="39"/>
-      <c r="P27"/>
-      <c r="Q27"/>
-      <c r="R27"/>
-      <c r="S27"/>
-      <c r="T27"/>
-    </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B28" s="34">
-        <v>6</v>
-      </c>
-      <c r="C28" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="D28" s="50"/>
-      <c r="E28" s="51"/>
-    </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B29" s="34">
-        <v>14</v>
-      </c>
-      <c r="C29" s="49" t="s">
-        <v>41</v>
-      </c>
-      <c r="D29" s="50"/>
-      <c r="E29" s="51"/>
-    </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B31" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="C31" s="40"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="R20:T20"/>
-    <mergeCell ref="R19:T19"/>
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="R17:T17"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="R21:T21"/>
     <mergeCell ref="D1:I1"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="Q8:S8"/>
@@ -2577,29 +2523,25 @@
     <mergeCell ref="Q10:S10"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C19:E19"/>
     <mergeCell ref="C12:E12"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="Q13:T13"/>
     <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="I6:O6"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="R20:T20"/>
+    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="R17:T17"/>
+    <mergeCell ref="C19:E19"/>
     <mergeCell ref="R16:T16"/>
-    <mergeCell ref="I6:O6"/>
     <mergeCell ref="R18:T18"/>
-    <mergeCell ref="C15:E15"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C8:E8"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="R21:T21"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C24:E24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2608,11 +2550,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC50"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.33203125" customWidth="1"/>
@@ -2629,7 +2571,6 @@
     <col min="13" max="13" width="5" customWidth="1"/>
     <col min="15" max="15" width="11.88671875" customWidth="1"/>
     <col min="16" max="17" width="8.88671875" customWidth="1"/>
-    <col min="21" max="21" width="8.88671875" style="36"/>
     <col min="22" max="22" width="9.109375" customWidth="1"/>
     <col min="23" max="25" width="2.109375" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="4.88671875" customWidth="1"/>
@@ -2638,177 +2579,177 @@
     <col min="29" max="29" width="5.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B1" s="11"/>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="48"/>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B3" s="76" t="s">
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="49"/>
+    </row>
+    <row r="3" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B3" s="96" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="48"/>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="49"/>
+    </row>
+    <row r="5" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B5" s="10"/>
     </row>
-    <row r="6" spans="1:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="65" t="s">
+    <row r="6" spans="2:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="99" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="C6" s="99" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="99" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="65" t="s">
+      <c r="E6" s="99" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="47"/>
-      <c r="J6" s="47"/>
-      <c r="K6" s="47"/>
-      <c r="L6" s="47"/>
-      <c r="M6" s="47"/>
-      <c r="N6" s="47"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="47"/>
-      <c r="Q6" s="47"/>
-      <c r="R6" s="47"/>
-      <c r="S6" s="47"/>
-      <c r="T6" s="47"/>
-      <c r="U6" s="47"/>
-      <c r="V6" s="47"/>
-      <c r="W6" s="47"/>
-      <c r="X6" s="47"/>
-      <c r="Y6" s="47"/>
-      <c r="Z6" s="47"/>
-      <c r="AA6" s="47"/>
-      <c r="AB6" s="47"/>
-      <c r="AC6" s="48"/>
-    </row>
-    <row r="7" spans="1:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="66"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="77" t="s">
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="48"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="48"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="48"/>
+      <c r="U6" s="48"/>
+      <c r="V6" s="48"/>
+      <c r="W6" s="48"/>
+      <c r="X6" s="48"/>
+      <c r="Y6" s="48"/>
+      <c r="Z6" s="48"/>
+      <c r="AA6" s="48"/>
+      <c r="AB6" s="48"/>
+      <c r="AC6" s="49"/>
+    </row>
+    <row r="7" spans="2:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="98"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="97" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="74" t="s">
+      <c r="F7" s="94" t="s">
         <v>48</v>
       </c>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47"/>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="47"/>
-      <c r="N7" s="47"/>
-      <c r="O7" s="48"/>
-      <c r="P7" s="73" t="s">
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="49"/>
+      <c r="P7" s="93" t="s">
         <v>49</v>
       </c>
-      <c r="Q7" s="47"/>
-      <c r="R7" s="47"/>
-      <c r="S7" s="47"/>
-      <c r="T7" s="47"/>
-      <c r="U7" s="47"/>
-      <c r="V7" s="48"/>
-      <c r="W7" s="71" t="s">
+      <c r="Q7" s="48"/>
+      <c r="R7" s="48"/>
+      <c r="S7" s="48"/>
+      <c r="T7" s="48"/>
+      <c r="U7" s="48"/>
+      <c r="V7" s="49"/>
+      <c r="W7" s="103" t="s">
         <v>50</v>
       </c>
-      <c r="X7" s="72"/>
-      <c r="Y7" s="72"/>
-      <c r="Z7" s="72"/>
-      <c r="AA7" s="72"/>
-      <c r="AB7" s="72"/>
-      <c r="AC7" s="45"/>
-    </row>
-    <row r="8" spans="1:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="66"/>
-      <c r="C8" s="75" t="s">
+      <c r="X7" s="104"/>
+      <c r="Y7" s="104"/>
+      <c r="Z7" s="104"/>
+      <c r="AA7" s="104"/>
+      <c r="AB7" s="104"/>
+      <c r="AC7" s="39"/>
+    </row>
+    <row r="8" spans="2:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="98"/>
+      <c r="C8" s="95" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="75" t="s">
+      <c r="D8" s="95" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="66"/>
-      <c r="F8" s="74" t="s">
+      <c r="E8" s="98"/>
+      <c r="F8" s="94" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="48"/>
-      <c r="H8" s="74" t="s">
+      <c r="G8" s="49"/>
+      <c r="H8" s="94" t="s">
         <v>53</v>
       </c>
-      <c r="I8" s="48"/>
-      <c r="J8" s="74" t="s">
+      <c r="I8" s="49"/>
+      <c r="J8" s="94" t="s">
         <v>54</v>
       </c>
-      <c r="K8" s="48"/>
-      <c r="L8" s="74" t="s">
+      <c r="K8" s="49"/>
+      <c r="L8" s="94" t="s">
         <v>55</v>
       </c>
-      <c r="M8" s="48"/>
-      <c r="N8" s="74" t="s">
+      <c r="M8" s="49"/>
+      <c r="N8" s="94" t="s">
         <v>56</v>
       </c>
-      <c r="O8" s="48"/>
-      <c r="P8" s="73" t="s">
+      <c r="O8" s="49"/>
+      <c r="P8" s="93" t="s">
         <v>57</v>
       </c>
-      <c r="Q8" s="73" t="s">
+      <c r="Q8" s="93" t="s">
         <v>58</v>
       </c>
-      <c r="R8" s="73" t="s">
+      <c r="R8" s="93" t="s">
         <v>59</v>
       </c>
-      <c r="S8" s="73" t="s">
+      <c r="S8" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="T8" s="69" t="s">
+      <c r="T8" s="101" t="s">
+        <v>168</v>
+      </c>
+      <c r="U8" s="93" t="s">
         <v>169</v>
       </c>
-      <c r="U8" s="73" t="s">
-        <v>170</v>
-      </c>
-      <c r="V8" s="68">
+      <c r="V8" s="100">
         <v>0</v>
       </c>
-      <c r="W8" s="68">
+      <c r="W8" s="100">
         <v>1</v>
       </c>
-      <c r="X8" s="68">
+      <c r="X8" s="100">
         <v>2</v>
       </c>
-      <c r="Y8" s="68" t="s">
+      <c r="Y8" s="100" t="s">
         <v>61</v>
       </c>
-      <c r="Z8" s="68" t="s">
+      <c r="Z8" s="100" t="s">
         <v>62</v>
       </c>
-      <c r="AA8" s="68" t="s">
+      <c r="AA8" s="100" t="s">
         <v>63</v>
       </c>
-      <c r="AB8" s="68" t="s">
+      <c r="AB8" s="100" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="67"/>
-      <c r="C9" s="67"/>
-      <c r="D9" s="67"/>
-      <c r="E9" s="67"/>
+    <row r="9" spans="2:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="55"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
       <c r="F9" s="12" t="s">
         <v>65</v>
       </c>
@@ -2839,22 +2780,21 @@
       <c r="O9" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="P9" s="67"/>
-      <c r="Q9" s="67"/>
-      <c r="R9" s="67"/>
-      <c r="S9" s="67"/>
-      <c r="T9" s="70"/>
-      <c r="U9" s="67"/>
-      <c r="V9" s="67"/>
-      <c r="W9" s="67"/>
-      <c r="X9" s="67"/>
-      <c r="Y9" s="67"/>
-      <c r="Z9" s="67"/>
-      <c r="AA9" s="67"/>
-      <c r="AB9" s="67"/>
-    </row>
-    <row r="10" spans="1:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
+      <c r="P9" s="55"/>
+      <c r="Q9" s="55"/>
+      <c r="R9" s="55"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="102"/>
+      <c r="U9" s="55"/>
+      <c r="V9" s="55"/>
+      <c r="W9" s="55"/>
+      <c r="X9" s="55"/>
+      <c r="Y9" s="55"/>
+      <c r="Z9" s="55"/>
+      <c r="AA9" s="55"/>
+      <c r="AB9" s="55"/>
+    </row>
+    <row r="10" spans="2:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="13" t="s">
         <v>67</v>
       </c>
@@ -2936,10 +2876,8 @@
       <c r="AB10" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="AC10" s="36"/>
-    </row>
-    <row r="11" spans="1:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36"/>
+    </row>
+    <row r="11" spans="2:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="13" t="s">
         <v>73</v>
       </c>
@@ -2950,7 +2888,7 @@
         <v>75</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F11" s="16" t="s">
         <v>72</v>
@@ -3021,21 +2959,19 @@
       <c r="AB11" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="AC11" s="36"/>
-    </row>
-    <row r="12" spans="1:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="36"/>
+    </row>
+    <row r="12" spans="2:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="43" t="s">
+      <c r="D12" s="37" t="s">
         <v>75</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>72</v>
@@ -3106,10 +3042,8 @@
       <c r="AB12" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="AC12" s="36"/>
-    </row>
-    <row r="13" spans="1:29" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
+    </row>
+    <row r="13" spans="2:29" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="13" t="s">
         <v>78</v>
       </c>
@@ -3120,7 +3054,7 @@
         <v>75</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F13" s="16" t="s">
         <v>72</v>
@@ -3191,10 +3125,8 @@
       <c r="AB13" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="AC13" s="36"/>
-    </row>
-    <row r="14" spans="1:29" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="36"/>
+    </row>
+    <row r="14" spans="2:29" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="13" t="s">
         <v>80</v>
       </c>
@@ -3205,7 +3137,7 @@
         <v>82</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F14" s="16" t="s">
         <v>72</v>
@@ -3276,10 +3208,8 @@
       <c r="AB14" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="AC14" s="36"/>
-    </row>
-    <row r="15" spans="1:29" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="36"/>
+    </row>
+    <row r="15" spans="2:29" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="s">
         <v>83</v>
       </c>
@@ -3290,7 +3220,7 @@
         <v>75</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F15" s="16" t="s">
         <v>72</v>
@@ -3361,10 +3291,8 @@
       <c r="AB15" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="AC15" s="36"/>
-    </row>
-    <row r="16" spans="1:29" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="36"/>
+    </row>
+    <row r="16" spans="2:29" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="13" t="s">
         <v>85</v>
       </c>
@@ -3375,7 +3303,7 @@
         <v>75</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F16" s="16" t="s">
         <v>72</v>
@@ -3446,10 +3374,8 @@
       <c r="AB16" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="AC16" s="36"/>
-    </row>
-    <row r="17" spans="1:29" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="36"/>
+    </row>
+    <row r="17" spans="1:28" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B17" s="13" t="s">
         <v>87</v>
       </c>
@@ -3460,7 +3386,7 @@
         <v>82</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F17" s="16" t="s">
         <v>72</v>
@@ -3531,10 +3457,8 @@
       <c r="AB17" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="AC17" s="36"/>
-    </row>
-    <row r="18" spans="1:29" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
+    </row>
+    <row r="18" spans="1:28" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B18" s="13" t="s">
         <v>89</v>
       </c>
@@ -3545,7 +3469,7 @@
         <v>75</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F18" s="16" t="s">
         <v>72</v>
@@ -3616,10 +3540,8 @@
       <c r="AB18" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="AC18" s="36"/>
-    </row>
-    <row r="19" spans="1:29" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="36"/>
+    </row>
+    <row r="19" spans="1:28" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="s">
         <v>91</v>
       </c>
@@ -3630,7 +3552,7 @@
         <v>75</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F19" s="16" t="s">
         <v>72</v>
@@ -3701,146 +3623,108 @@
       <c r="AB19" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="AC19" s="36"/>
-    </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A23" s="36" t="s">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A24" s="36" t="s">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A25" s="36"/>
-    </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A26" s="36" t="s">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A27" s="36" t="s">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A28" s="36" t="s">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A29" s="36"/>
-    </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A30" s="36" t="s">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A31" s="36" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A32" s="36"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="36"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="36" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="36" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="36" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="36"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="36" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="36"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="36"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="36"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="36"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="36" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="36" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="36"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="36" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="36" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="36"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="36"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="36" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="36"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="36"/>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="36"/>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="36"/>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="W7:AB7"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="W8:W9"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="S8:S9"/>
     <mergeCell ref="L8:M8"/>
@@ -3857,33 +3741,19 @@
     <mergeCell ref="P8:P9"/>
     <mergeCell ref="AB8:AB9"/>
     <mergeCell ref="V8:V9"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="W7:AB7"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="W8:W9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B1:N21"/>
+  <dimension ref="B1:N29"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
@@ -3901,47 +3771,47 @@
   <sheetData>
     <row r="1" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B1" s="11"/>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="49"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="94" t="s">
+      <c r="B3" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="96"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="42"/>
     </row>
     <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="89" t="s">
+      <c r="B4" s="75" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="80" t="s">
+      <c r="C4" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="98" t="s">
+      <c r="D4" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="78" t="s">
+      <c r="E4" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="79"/>
-      <c r="G4" s="82" t="s">
+      <c r="F4" s="68"/>
+      <c r="G4" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="H4" s="48"/>
+      <c r="H4" s="49"/>
     </row>
     <row r="5" spans="2:12" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="90"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="99"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="46"/>
       <c r="E5" s="2" t="s">
         <v>99</v>
       </c>
@@ -3959,7 +3829,7 @@
       <c r="B6" s="19">
         <v>1</v>
       </c>
-      <c r="C6" s="112" t="s">
+      <c r="C6" s="65" t="s">
         <v>103</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -3982,7 +3852,7 @@
       <c r="B7" s="19">
         <v>2</v>
       </c>
-      <c r="C7" s="113"/>
+      <c r="C7" s="66"/>
       <c r="D7" s="4" t="s">
         <v>76</v>
       </c>
@@ -4003,7 +3873,7 @@
       <c r="B8" s="19">
         <v>3</v>
       </c>
-      <c r="C8" s="113"/>
+      <c r="C8" s="66"/>
       <c r="D8" s="9" t="s">
         <v>80</v>
       </c>
@@ -4024,7 +3894,7 @@
       <c r="B9" s="19">
         <v>4</v>
       </c>
-      <c r="C9" s="113"/>
+      <c r="C9" s="66"/>
       <c r="D9" s="9" t="s">
         <v>83</v>
       </c>
@@ -4042,107 +3912,107 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="37">
+      <c r="B10" s="19">
         <v>5</v>
       </c>
-      <c r="C10" s="113"/>
-      <c r="D10" s="37" t="s">
+      <c r="C10" s="66"/>
+      <c r="D10" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="F10" s="37" t="s">
+      <c r="F10" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="G10" s="37" t="s">
+      <c r="G10" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="37" t="s">
+      <c r="H10" s="19" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="2:12" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="20">
         <v>6</v>
       </c>
-      <c r="C11" s="113"/>
-      <c r="D11" s="37" t="s">
+      <c r="C11" s="66"/>
+      <c r="D11" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="F11" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="G11" s="37" t="b">
+      <c r="E11" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" s="19" t="b">
         <v>1</v>
       </c>
-      <c r="H11" s="37" t="b">
+      <c r="H11" s="19" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:12" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="20">
         <v>7</v>
       </c>
-      <c r="C12" s="113"/>
-      <c r="D12" s="37" t="s">
+      <c r="C12" s="66"/>
+      <c r="D12" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="E12" s="37" t="s">
+      <c r="E12" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="F12" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="F12" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="G12" s="37" t="b">
+      <c r="G12" s="19" t="b">
         <v>1</v>
       </c>
-      <c r="H12" s="37" t="b">
+      <c r="H12" s="19" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="2:12" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="20">
         <v>8</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="37" t="s">
+      <c r="C13" s="66"/>
+      <c r="D13" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E13" s="37" t="s">
+      <c r="E13" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="F13" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="F13" s="37" t="s">
-        <v>180</v>
-      </c>
-      <c r="G13" s="37" t="b">
+      <c r="G13" s="19" t="b">
         <v>0</v>
       </c>
-      <c r="H13" s="37" t="b">
+      <c r="H13" s="19" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:12" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="20">
         <v>9</v>
       </c>
-      <c r="C14" s="113"/>
-      <c r="D14" s="37" t="s">
+      <c r="C14" s="66"/>
+      <c r="D14" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E14" s="37" t="s">
+      <c r="E14" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="F14" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="G14" s="37" t="b">
+      <c r="F14" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="G14" s="19" t="b">
         <v>1</v>
       </c>
-      <c r="H14" s="37" t="b">
+      <c r="H14" s="19" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4150,20 +4020,20 @@
       <c r="B15" s="20">
         <v>10</v>
       </c>
-      <c r="C15" s="113"/>
-      <c r="D15" s="37" t="s">
+      <c r="C15" s="66"/>
+      <c r="D15" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="E15" s="37" t="s">
-        <v>183</v>
-      </c>
-      <c r="F15" s="37" t="s">
+      <c r="E15" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="G15" s="37" t="b">
+      <c r="F15" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="G15" s="19" t="b">
         <v>1</v>
       </c>
-      <c r="H15" s="114" t="b">
+      <c r="H15" s="19" t="b">
         <v>1</v>
       </c>
       <c r="I15" s="3"/>
@@ -4171,175 +4041,376 @@
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
     </row>
-    <row r="16" spans="2:12" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="111"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="19">
+        <v>11</v>
+      </c>
+      <c r="C16" s="66"/>
+      <c r="D16" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>195</v>
+      </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="19">
+        <v>12</v>
+      </c>
+      <c r="C17" s="66"/>
+      <c r="D17" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="19">
+        <v>13</v>
+      </c>
+      <c r="C18" s="66"/>
+      <c r="D18" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="19">
+        <v>14</v>
+      </c>
+      <c r="C19" s="66"/>
+      <c r="D19" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="19">
+        <v>15</v>
+      </c>
+      <c r="C20" s="66"/>
+      <c r="D20" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="20">
+        <v>16</v>
+      </c>
+      <c r="C21" s="66"/>
+      <c r="D21" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="20">
+        <v>17</v>
+      </c>
+      <c r="C22" s="66"/>
+      <c r="D22" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="20">
+        <v>18</v>
+      </c>
+      <c r="C23" s="66"/>
+      <c r="D23" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="K17" s="21"/>
-    </row>
-    <row r="18" spans="2:14" ht="15.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="91" t="s">
+      <c r="K25" s="21"/>
+    </row>
+    <row r="26" spans="2:14" ht="15.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="77" t="s">
         <v>112</v>
       </c>
-      <c r="C18" s="92"/>
-      <c r="D18" s="92"/>
-      <c r="E18" s="92"/>
-      <c r="F18" s="107" t="s">
+      <c r="C26" s="62"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="60" t="s">
         <v>113</v>
       </c>
-      <c r="G18" s="103"/>
-      <c r="H18" s="108" t="s">
+      <c r="G26" s="53"/>
+      <c r="H26" s="61" t="s">
         <v>114</v>
       </c>
-      <c r="I18" s="92"/>
-      <c r="J18" s="92"/>
-      <c r="K18" s="92"/>
-      <c r="L18" s="109"/>
-      <c r="M18" s="102" t="s">
+      <c r="I26" s="62"/>
+      <c r="J26" s="62"/>
+      <c r="K26" s="62"/>
+      <c r="L26" s="63"/>
+      <c r="M26" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="N18" s="103"/>
-    </row>
-    <row r="19" spans="2:14" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="83" t="s">
+      <c r="N26" s="53"/>
+    </row>
+    <row r="27" spans="2:14" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="72" t="s">
         <v>116</v>
       </c>
-      <c r="C19" s="88" t="s">
+      <c r="C27" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="D19" s="88" t="s">
+      <c r="D27" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="E19" s="93" t="s">
+      <c r="E27" s="78" t="s">
         <v>119</v>
       </c>
-      <c r="F19" s="110" t="s">
+      <c r="F27" s="64" t="s">
         <v>120</v>
       </c>
-      <c r="G19" s="100" t="s">
+      <c r="G27" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="H19" s="87" t="s">
+      <c r="H27" s="74" t="s">
         <v>122</v>
       </c>
-      <c r="I19" s="88" t="s">
+      <c r="I27" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="J19" s="88" t="s">
+      <c r="J27" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="K19" s="104" t="s">
+      <c r="K27" s="56" t="s">
         <v>123</v>
       </c>
-      <c r="L19" s="85" t="s">
+      <c r="L27" s="73" t="s">
         <v>124</v>
       </c>
-      <c r="M19" s="106" t="s">
+      <c r="M27" s="58" t="s">
         <v>125</v>
       </c>
-      <c r="N19" s="97" t="s">
+      <c r="N27" s="43" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B20" s="84"/>
-      <c r="C20" s="67"/>
-      <c r="D20" s="67"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="86"/>
-      <c r="G20" s="101"/>
-      <c r="H20" s="84"/>
-      <c r="I20" s="67"/>
-      <c r="J20" s="67"/>
-      <c r="K20" s="105"/>
-      <c r="L20" s="86"/>
-      <c r="M20" s="84"/>
-      <c r="N20" s="86"/>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B21" s="25">
-        <f>SUM(C21:D21)</f>
-        <v>10</v>
-      </c>
-      <c r="C21" s="22">
-        <v>10</v>
-      </c>
-      <c r="D21" s="22">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B28" s="59"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="55"/>
+      <c r="K28" s="57"/>
+      <c r="L28" s="44"/>
+      <c r="M28" s="59"/>
+      <c r="N28" s="44"/>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B29" s="24">
+        <f>SUM(C29:D29)</f>
+        <v>18</v>
+      </c>
+      <c r="C29" s="22">
+        <v>18</v>
+      </c>
+      <c r="D29" s="22">
         <v>0</v>
       </c>
-      <c r="E21" s="23" t="s">
+      <c r="E29" s="105">
+        <v>1</v>
+      </c>
+      <c r="F29" s="23">
+        <v>0</v>
+      </c>
+      <c r="G29" s="8">
+        <v>0</v>
+      </c>
+      <c r="H29" s="7">
+        <v>0</v>
+      </c>
+      <c r="I29" s="24">
+        <f>SUM(J29:K29)</f>
+        <v>18</v>
+      </c>
+      <c r="J29" s="22">
+        <v>18</v>
+      </c>
+      <c r="K29" s="25">
+        <v>0</v>
+      </c>
+      <c r="L29" s="106">
+        <v>1</v>
+      </c>
+      <c r="M29" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="F21" s="24">
-        <v>0</v>
-      </c>
-      <c r="G21" s="8">
-        <v>0</v>
-      </c>
-      <c r="H21" s="7">
-        <v>0</v>
-      </c>
-      <c r="I21" s="25">
-        <f>SUM(J21:K21)</f>
-        <v>10</v>
-      </c>
-      <c r="J21" s="22">
-        <v>10</v>
-      </c>
-      <c r="K21" s="26">
-        <v>0</v>
-      </c>
-      <c r="L21" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="M21" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="N21" s="28">
-        <f>C21</f>
-        <v>10</v>
+      <c r="N29" s="26">
+        <f>C29</f>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="L27:L28"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="C6:C23"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="N27:N28"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="D1:G1"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="K19:K20"/>
-    <mergeCell ref="M19:M20"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:L18"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="C6:C15"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="K27:K28"/>
+    <mergeCell ref="M27:M28"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:L26"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="F27:F28"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="C4:C5"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="L19:L20"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="E19:E20"/>
   </mergeCells>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
